--- a/hardis-report/xls/backup-updated-files-monitoring_d700000009o68eae_dev_ed.xlsx
+++ b/hardis-report/xls/backup-updated-files-monitoring_d700000009o68eae_dev_ed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
   <si>
     <t>File</t>
   </si>
@@ -52,10 +52,43 @@
     <t>📰</t>
   </si>
   <si>
+    <t>notificationTypeConfig/NotificationTypeConfig.config-meta.xml</t>
+  </si>
+  <si>
+    <t>NotificationTypeConfig NotificationTypeConfig</t>
+  </si>
+  <si>
     <t>scontrols/Feed.scf</t>
   </si>
   <si>
     <t>Scontrol Feed</t>
+  </si>
+  <si>
+    <t>settings/CustomerIntelligence.settings-meta.xml</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Settings CustomerIntelligence</t>
+  </si>
+  <si>
+    <t>settings/IncidentMgmt.settings-meta.xml</t>
+  </si>
+  <si>
+    <t>Settings IncidentMgmt</t>
+  </si>
+  <si>
+    <t>settings/SelfService.settings-meta.xml</t>
+  </si>
+  <si>
+    <t>Settings SelfService</t>
+  </si>
+  <si>
+    <t>manifest/package-all-org-items.xml</t>
+  </si>
+  <si>
+    <t>manifest/package-backup-items.xml</t>
   </si>
 </sst>
 </file>
@@ -117,8 +150,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G3" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:G3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G9" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:G9">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
     <filterColumn colId="2" hiddenButton="0"/>
@@ -462,12 +495,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -519,7 +552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -539,6 +572,144 @@
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
     </row>

--- a/hardis-report/xls/backup-updated-files-monitoring_d700000009o68eae_dev_ed.xlsx
+++ b/hardis-report/xls/backup-updated-files-monitoring_d700000009o68eae_dev_ed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>File</t>
   </si>
@@ -52,43 +52,10 @@
     <t>📰</t>
   </si>
   <si>
-    <t>notificationTypeConfig/NotificationTypeConfig.config-meta.xml</t>
-  </si>
-  <si>
-    <t>NotificationTypeConfig NotificationTypeConfig</t>
-  </si>
-  <si>
     <t>scontrols/Feed.scf</t>
   </si>
   <si>
     <t>Scontrol Feed</t>
-  </si>
-  <si>
-    <t>settings/CustomerIntelligence.settings-meta.xml</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Settings CustomerIntelligence</t>
-  </si>
-  <si>
-    <t>settings/IncidentMgmt.settings-meta.xml</t>
-  </si>
-  <si>
-    <t>Settings IncidentMgmt</t>
-  </si>
-  <si>
-    <t>settings/SelfService.settings-meta.xml</t>
-  </si>
-  <si>
-    <t>Settings SelfService</t>
-  </si>
-  <si>
-    <t>manifest/package-all-org-items.xml</t>
-  </si>
-  <si>
-    <t>manifest/package-backup-items.xml</t>
   </si>
 </sst>
 </file>
@@ -150,8 +117,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G9" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:G9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table_sheet1_1" displayName="Table_sheet1_1" ref="A1:G3" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:G3">
     <filterColumn colId="0" hiddenButton="0"/>
     <filterColumn colId="1" hiddenButton="0"/>
     <filterColumn colId="2" hiddenButton="0"/>
@@ -495,12 +462,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -552,7 +519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -572,144 +539,6 @@
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
